--- a/mock_data/mvp2a3_core.xlsx
+++ b/mock_data/mvp2a3_core.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>中国银行上海分行</t>
+          <t>六盘水银行海门分行</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>招商银行上海分行</t>
+          <t>邯郸银行合肥分行</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>中国银行上海分行</t>
+          <t>六盘水银行海门分行</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>招商银行上海分行</t>
+          <t>邯郸银行合肥分行</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">

--- a/mock_data/mvp2a3_core.xlsx
+++ b/mock_data/mvp2a3_core.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BC3001</t>
+          <t>BCN0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:05:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>六盘水银行海门分行</t>
+          <t>上海银行浦东分行</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -645,23 +645,23 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>88.8</v>
+        <v>63.25</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>88.8</v>
+        <v>63.25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>20088.8</v>
+        <v>20163.25</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-10 10:00:00</t>
+          <t>2026-06-11 11:05:00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6214********3001</t>
+          <t>6214********5001</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>杭州清河商贸有限公司</t>
+          <t>恩悌网络有限公司</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>邯郸银行合肥分行</t>
+          <t>太原银行石家庄分行</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>清算正常配平</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MVP-2a3 正常配平样例</t>
+          <t>清算批次正常自动平账样例</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -741,27 +741,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CORE3003</t>
+          <t>BCN0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B202606110003</t>
+          <t>B202606100002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:05:00</t>
+          <t>12:10:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>六盘水银行海门分行</t>
+          <t>上海银行浦东分行</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -795,106 +795,1906 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>150</v>
+        <v>76.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>150</v>
+        <v>76.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>20276.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-12 12:10:00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6214********5002</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>易动力信息有限公司</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>通辽银行荆门分行</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>小王那笔材料钱</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BCN0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B202606100003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20389.75</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:15:00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6214********5003</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>佳禾科技有限公司</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>长春银行石家庄分行</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>支付物流运输费用</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BCN0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B202606100004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>103</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>103</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>20503</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-14 14:20:00</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6214********5004</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>兰金电子网络有限公司</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>哈尔滨银行淮安分行</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>供应商催的那笔</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BCN0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B202606100005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15:25:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>20616.25</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:25:00</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6214********5005</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>易动力网络有限公司</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>长春银行哈尔滨分行</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BCN0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B202606100006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20729.5</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-11 16:30:00</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6214********5006</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>联软科技有限公司</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>拉萨银行汕尾分行</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>门店今天的款补上</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BCN0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B202606100007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>17:35:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20842.75</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:35:00</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6214********5007</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>凌颖信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>贵阳银行哈尔滨分行</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BCN0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B202606100008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>156</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>156</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20956</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-13 10:40:00</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6214********5008</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>思优网络有限公司</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>通辽银行齐齐哈尔分行</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>小王那笔材料钱</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BCN0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B202606100009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21069.25</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-14 11:45:00</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6214********5009</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>国讯科技有限公司</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>潜江银行广州分行</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BCN0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B202606100010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21182.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:50:00</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6214********5010</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>商软冠联科技有限公司</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>北镇银行宜都分行</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BCN0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B202606100011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21295.75</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-11 13:55:00</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6214********5011</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>立信电子传媒有限公司</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>郑州银行石家庄分行</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BCN0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B202606100012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>209</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>209</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21409</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-12 14:00:00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6214********5012</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>东方峻景网络有限公司</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>银川银行昆明分行</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BC3001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B202606100001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20088.8</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:00:00</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6214********3001</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>杭州清河商贸有限公司</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>邯郸银行海口分行</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>收到项目阶段验收款</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>MVP-2a3 正常配平样例</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CORE3003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B202606110003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:05:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>150</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>150</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>20238.8</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2026-06-11 09:05:00</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>上海晨星贸易有限公司</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>6214********3003</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>苏州清源零售有限公司</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>邯郸银行合肥分行</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>兴安盟银行重庆分行</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>清算平台</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>跨日切 T+1 核心补记</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>往来款</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>门店收款</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>POSTED</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>SH001</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>CLEARING_SYS</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>TRF_IN</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>CLEARING_PLATFORM</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>MVP-2a3 跨日切命中样例</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>VCH3003</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>REF3003</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>ORD3003</t>
         </is>

--- a/mock_data/mvp2a3_core.xlsx
+++ b/mock_data/mvp2a3_core.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BC3001</t>
+          <t>BCN0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>11:05:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>中国银行上海分行</t>
+          <t>上海银行浦东分行</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -645,23 +645,23 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>88.8</v>
+        <v>63.25</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>88.8</v>
+        <v>63.25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>20088.8</v>
+        <v>20163.25</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-10 10:00:00</t>
+          <t>2026-06-11 11:05:00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6214********3001</t>
+          <t>6214********5001</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>杭州清河商贸有限公司</t>
+          <t>恩悌网络有限公司</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>招商银行上海分行</t>
+          <t>太原银行石家庄分行</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>清算正常配平</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MVP-2a3 正常配平样例</t>
+          <t>清算批次正常自动平账样例</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -741,27 +741,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CORE3003</t>
+          <t>BCN0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B202606110003</t>
+          <t>B202606100002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:05:00</t>
+          <t>12:10:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>中国银行上海分行</t>
+          <t>上海银行浦东分行</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -795,106 +795,1906 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>150</v>
+        <v>76.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>150</v>
+        <v>76.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>20276.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-12 12:10:00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6214********5002</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>易动力信息有限公司</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>通辽银行荆门分行</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>小王那笔材料钱</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BCN0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B202606100003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20389.75</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:15:00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6214********5003</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>佳禾科技有限公司</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>长春银行石家庄分行</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>支付物流运输费用</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BCN0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B202606100004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>103</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>103</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>20503</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-14 14:20:00</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6214********5004</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>兰金电子网络有限公司</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>哈尔滨银行淮安分行</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>供应商催的那笔</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BCN0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B202606100005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15:25:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>20616.25</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:25:00</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6214********5005</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>易动力网络有限公司</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>长春银行哈尔滨分行</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BCN0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B202606100006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20729.5</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-11 16:30:00</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6214********5006</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>联软科技有限公司</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>拉萨银行汕尾分行</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>门店今天的款补上</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BCN0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B202606100007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>17:35:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20842.75</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:35:00</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6214********5007</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>凌颖信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>贵阳银行哈尔滨分行</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BCN0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B202606100008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>156</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>156</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20956</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-13 10:40:00</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6214********5008</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>思优网络有限公司</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>通辽银行齐齐哈尔分行</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>小王那笔材料钱</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BCN0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B202606100009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21069.25</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-14 11:45:00</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6214********5009</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>国讯科技有限公司</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>潜江银行广州分行</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BCN0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B202606100010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21182.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:50:00</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6214********5010</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>商软冠联科技有限公司</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>北镇银行宜都分行</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BCN0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B202606100011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21295.75</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-11 13:55:00</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6214********5011</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>立信电子传媒有限公司</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>郑州银行石家庄分行</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BCN0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B202606100012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>209</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>209</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21409</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-12 14:00:00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6214********5012</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>东方峻景网络有限公司</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>银川银行昆明分行</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>清算批次正常自动平账样例</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BC3001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B202606100001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20088.8</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:00:00</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6214********3001</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>杭州清河商贸有限公司</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>邯郸银行海口分行</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>清算平台</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>收到项目阶段验收款</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>门店收款</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>POSTED</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>SH001</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>CLEARING_SYS</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>TRF_IN</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>CLEARING_PLATFORM</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>MVP-2a3 正常配平样例</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CORE3003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B202606110003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:05:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>上海银行浦东分行</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TRANSFER_IN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>150</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>150</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>20238.8</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2026-06-11 09:05:00</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>上海晨星贸易有限公司</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>6214********3003</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>苏州清源零售有限公司</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>招商银行上海分行</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>兴安盟银行重庆分行</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>清算平台</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>跨日切 T+1 核心补记</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>往来款</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>门店收款</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>POSTED</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>SH001</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>CLEARING_SYS</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>TRF_IN</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>CLEARING_PLATFORM</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>MVP-2a3 跨日切命中样例</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>VCH3003</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>REF3003</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>ORD3003</t>
         </is>

--- a/mock_data/mvp2a3_core.xlsx
+++ b/mock_data/mvp2a3_core.xlsx
@@ -734,9 +734,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v/>
+      </c>
+      <c r="AG2" t="n">
+        <v/>
+      </c>
+      <c r="AH2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -884,9 +890,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1034,9 +1046,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1184,9 +1202,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1334,9 +1358,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1484,9 +1514,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1634,9 +1670,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1784,9 +1826,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1934,9 +1982,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2084,9 +2138,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2234,9 +2294,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2384,9 +2450,15 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2534,9 +2606,15 @@
           <t>MVP-2a3 正常配平样例</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/mock_data/mvp2a3_core.xlsx
+++ b/mock_data/mvp2a3_core.xlsx
@@ -734,15 +734,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v/>
-      </c>
-      <c r="AG2" t="n">
-        <v/>
-      </c>
-      <c r="AH2" t="n">
-        <v/>
-      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -890,15 +884,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1046,15 +1034,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1202,15 +1184,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1358,15 +1334,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1514,15 +1484,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1670,15 +1634,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1826,15 +1784,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1982,15 +1934,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2138,15 +2084,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF11" t="n">
-        <v/>
-      </c>
-      <c r="AG11" t="n">
-        <v/>
-      </c>
-      <c r="AH11" t="n">
-        <v/>
-      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2294,15 +2234,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF12" t="n">
-        <v/>
-      </c>
-      <c r="AG12" t="n">
-        <v/>
-      </c>
-      <c r="AH12" t="n">
-        <v/>
-      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2450,15 +2384,9 @@
           <t>清算批次正常自动平账样例</t>
         </is>
       </c>
-      <c r="AF13" t="n">
-        <v/>
-      </c>
-      <c r="AG13" t="n">
-        <v/>
-      </c>
-      <c r="AH13" t="n">
-        <v/>
-      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2606,15 +2534,9 @@
           <t>MVP-2a3 正常配平样例</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v/>
-      </c>
-      <c r="AG14" t="n">
-        <v/>
-      </c>
-      <c r="AH14" t="n">
-        <v/>
-      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
